--- a/Varun Beverages.xlsx
+++ b/Varun Beverages.xlsx
@@ -5,19 +5,19 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\mock data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\varun beverages\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C85D74EF-160A-44A4-AB2D-C1CCADD11040}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7555BAD2-A567-48AC-BD5F-96AF8A2B417B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="5" xr2:uid="{DC4468AB-D1B0-41A7-9804-C13850339D52}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{DC4468AB-D1B0-41A7-9804-C13850339D52}"/>
   </bookViews>
   <sheets>
     <sheet name="Summary " sheetId="7" r:id="rId1"/>
-    <sheet name="Dashboard " sheetId="5" r:id="rId2"/>
-    <sheet name="Ratio Analysis" sheetId="6" r:id="rId3"/>
-    <sheet name="Assumptions" sheetId="1" r:id="rId4"/>
-    <sheet name="Calculations " sheetId="4" r:id="rId5"/>
+    <sheet name="Calculations " sheetId="4" r:id="rId2"/>
+    <sheet name="Dashboard " sheetId="5" r:id="rId3"/>
+    <sheet name="Ratio Analysis" sheetId="6" r:id="rId4"/>
+    <sheet name="Assumptions" sheetId="1" r:id="rId5"/>
     <sheet name="Raw Data " sheetId="2" r:id="rId6"/>
     <sheet name="Data Sheet " sheetId="3" r:id="rId7"/>
   </sheets>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="107">
   <si>
     <t>Revenue Drivers (Operational Inputs)</t>
   </si>
@@ -363,6 +363,9 @@
   </si>
   <si>
     <t>N/a</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Varun Beverages Ltd </t>
   </si>
 </sst>
 </file>
@@ -634,7 +637,7 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="57">
+  <cellXfs count="58">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -705,6 +708,9 @@
     </xf>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -3010,14 +3016,14 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>152400</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>137160</xdr:rowOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>121920</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
       <xdr:colOff>601980</xdr:colOff>
-      <xdr:row>21</xdr:row>
-      <xdr:rowOff>68580</xdr:rowOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>53340</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -3032,7 +3038,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="152400" y="320040"/>
+          <a:off x="152400" y="502920"/>
           <a:ext cx="6096000" cy="3589020"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -4299,18 +4305,313 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3438B05D-D8CC-446E-A200-C03BEAB4FA4F}">
-  <dimension ref="A1"/>
+  <dimension ref="B2:K2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="2.33203125" customWidth="1"/>
   </cols>
-  <sheetData/>
+  <sheetData>
+    <row r="2" spans="2:11" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B2" s="47" t="s">
+        <v>106</v>
+      </c>
+      <c r="C2" s="47"/>
+      <c r="D2" s="47"/>
+      <c r="E2" s="47"/>
+      <c r="F2" s="47"/>
+      <c r="G2" s="47"/>
+      <c r="H2" s="47"/>
+      <c r="I2" s="47"/>
+      <c r="J2" s="47"/>
+      <c r="K2" s="47"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B2:K2"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3E9C427A-629E-4C27-87B4-21766E37E9D1}">
+  <dimension ref="A2:E23"/>
+  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="2.33203125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="56" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="18" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.88671875" style="1"/>
+    <col min="7" max="7" width="5.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="16384" width="8.88671875" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B2" s="42" t="s">
+        <v>79</v>
+      </c>
+      <c r="C2" s="43">
+        <v>46387</v>
+      </c>
+      <c r="D2" s="43">
+        <f>EDATE(C2,12)</f>
+        <v>46752</v>
+      </c>
+      <c r="E2" s="43">
+        <f>EDATE(D2,12)</f>
+        <v>47118</v>
+      </c>
+    </row>
+    <row r="3" spans="2:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B3" s="20" t="s">
+        <v>25</v>
+      </c>
+      <c r="C3" s="21"/>
+      <c r="D3" s="21"/>
+      <c r="E3" s="21"/>
+    </row>
+    <row r="4" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B4" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="C4" s="1">
+        <f>'Raw Data '!G3*(1+Assumptions!C5)</f>
+        <v>1358.5600000000002</v>
+      </c>
+      <c r="D4" s="11">
+        <f>C4*(1+Assumptions!C5)</f>
+        <v>1521.5872000000004</v>
+      </c>
+      <c r="E4" s="11">
+        <f>D4*(1+Assumptions!C5)</f>
+        <v>1704.1776640000005</v>
+      </c>
+    </row>
+    <row r="5" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B5" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="C5" s="19">
+        <f>'Raw Data '!G4*(1+Assumptions!C6)</f>
+        <v>182.35018466611703</v>
+      </c>
+      <c r="D5" s="19">
+        <f>C5*(1+Assumptions!C6)</f>
+        <v>185.99718835943938</v>
+      </c>
+      <c r="E5" s="19">
+        <f>D5*(1+Assumptions!C6)</f>
+        <v>189.71713212662817</v>
+      </c>
+    </row>
+    <row r="6" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B6" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="C6" s="19">
+        <f>C4*C5/10</f>
+        <v>24773.366687999998</v>
+      </c>
+      <c r="D6" s="19">
+        <f>D4*D5/10</f>
+        <v>28301.094104371201</v>
+      </c>
+      <c r="E6" s="19">
+        <f>E4*E5/10</f>
+        <v>32331.169904833667</v>
+      </c>
+    </row>
+    <row r="7" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B7" s="17" t="s">
+        <v>83</v>
+      </c>
+      <c r="C7" s="18"/>
+      <c r="D7" s="18"/>
+      <c r="E7" s="18"/>
+    </row>
+    <row r="8" spans="2:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B8" s="20" t="s">
+        <v>25</v>
+      </c>
+      <c r="C8" s="21"/>
+      <c r="D8" s="21"/>
+      <c r="E8" s="21"/>
+    </row>
+    <row r="9" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B9" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="C9" s="11">
+        <f>('Raw Data '!G3-'Raw Data '!F3)*'Raw Data '!F4</f>
+        <v>15842.356316725978</v>
+      </c>
+      <c r="D9" s="11">
+        <f>(D4-C4)*C5</f>
+        <v>29728.040025600036</v>
+      </c>
+      <c r="E9" s="11">
+        <f>(E4-D4)*D5</f>
+        <v>33961.312925245453</v>
+      </c>
+    </row>
+    <row r="10" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B10" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="C10" s="11">
+        <f>('Raw Data '!G4-'Raw Data '!F4)*'Raw Data '!G3</f>
+        <v>934.84368327397806</v>
+      </c>
+      <c r="D10" s="11">
+        <f>(D5-C5)*D4</f>
+        <v>5549.2341381120095</v>
+      </c>
+      <c r="E10" s="11">
+        <f>(E5-D5)*E4</f>
+        <v>6339.4450793791621</v>
+      </c>
+    </row>
+    <row r="11" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B11" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="C11" s="11">
+        <f>C9+C10</f>
+        <v>16777.199999999957</v>
+      </c>
+      <c r="D11" s="11">
+        <f t="shared" ref="D11:E11" si="0">D9+D10</f>
+        <v>35277.274163712049</v>
+      </c>
+      <c r="E11" s="11">
+        <f t="shared" si="0"/>
+        <v>40300.758004624615</v>
+      </c>
+    </row>
+    <row r="12" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B12" s="17" t="s">
+        <v>84</v>
+      </c>
+      <c r="C12" s="18"/>
+      <c r="D12" s="18"/>
+      <c r="E12" s="18"/>
+    </row>
+    <row r="13" spans="2:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B13" s="20" t="s">
+        <v>25</v>
+      </c>
+      <c r="C13" s="21"/>
+      <c r="D13" s="21"/>
+      <c r="E13" s="21"/>
+    </row>
+    <row r="14" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B14" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="C14" s="19">
+        <f>C6*Assumptions!C10</f>
+        <v>11148.0150096</v>
+      </c>
+      <c r="D14" s="19">
+        <f>$D$6*Assumptions!C10</f>
+        <v>12735.492346967041</v>
+      </c>
+      <c r="E14" s="19">
+        <f>$E$6*Assumptions!C10</f>
+        <v>14549.02645717515</v>
+      </c>
+    </row>
+    <row r="15" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B15" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="C15" s="19">
+        <f>C6*Assumptions!C11</f>
+        <v>2725.07033568</v>
+      </c>
+      <c r="D15" s="19">
+        <f>$D$6*Assumptions!C11</f>
+        <v>3113.1203514808321</v>
+      </c>
+      <c r="E15" s="19">
+        <f>$E$6*Assumptions!C11</f>
+        <v>3556.4286895317032</v>
+      </c>
+    </row>
+    <row r="16" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B16" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="C16" s="19">
+        <f>C6*Assumptions!C12</f>
+        <v>5202.4070044799992</v>
+      </c>
+      <c r="D16" s="19">
+        <f>$D$6*Assumptions!C12</f>
+        <v>5943.2297619179517</v>
+      </c>
+      <c r="E16" s="19">
+        <f>$E$6*Assumptions!C12</f>
+        <v>6789.5456800150696</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B17" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="C17" s="19">
+        <f>C6-(C14+C15+C16)</f>
+        <v>5697.8743382399989</v>
+      </c>
+      <c r="D17" s="19">
+        <f>D6-(D14+D15+D16)</f>
+        <v>6509.2516440053769</v>
+      </c>
+      <c r="E17" s="19">
+        <f>E6-(E14+E15+E16)</f>
+        <v>7436.1690781117431</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B18" s="22" t="s">
+        <v>89</v>
+      </c>
+      <c r="C18" s="23">
+        <f>C17/C6</f>
+        <v>0.22999999999999998</v>
+      </c>
+      <c r="D18" s="23">
+        <f>D17/D6</f>
+        <v>0.23</v>
+      </c>
+      <c r="E18" s="23">
+        <f>E17/E6</f>
+        <v>0.22999999999999998</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" ht="16.2" thickTop="1" x14ac:dyDescent="0.3"/>
+    <row r="21" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B21"/>
+      <c r="C21" s="27" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" ht="29.4" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>103</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="12" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4CE63FB2-9482-46F5-96F9-055ACEF11988}">
   <dimension ref="R10:W16"/>
   <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
@@ -4320,14 +4621,14 @@
   </cols>
   <sheetData>
     <row r="10" spans="18:23" x14ac:dyDescent="0.3">
-      <c r="R10" s="47" t="s">
+      <c r="R10" s="48" t="s">
         <v>104</v>
       </c>
-      <c r="S10" s="47"/>
-      <c r="T10" s="47"/>
-      <c r="U10" s="47"/>
-      <c r="V10" s="47"/>
-      <c r="W10" s="47"/>
+      <c r="S10" s="48"/>
+      <c r="T10" s="48"/>
+      <c r="U10" s="48"/>
+      <c r="V10" s="48"/>
+      <c r="W10" s="48"/>
     </row>
     <row r="11" spans="18:23" x14ac:dyDescent="0.3">
       <c r="R11" s="28">
@@ -4470,7 +4771,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C4ADC91-F7B2-4C44-ADE9-BE109BA4B8AA}">
   <dimension ref="B2:I10"/>
   <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
@@ -4482,22 +4783,22 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B2" s="48" t="s">
+      <c r="B2" s="49" t="s">
         <v>95</v>
       </c>
-      <c r="C2" s="48" t="s">
+      <c r="C2" s="49" t="s">
         <v>93</v>
       </c>
-      <c r="D2" s="48"/>
-      <c r="E2" s="48"/>
-      <c r="F2" s="48" t="s">
+      <c r="D2" s="49"/>
+      <c r="E2" s="49"/>
+      <c r="F2" s="49" t="s">
         <v>94</v>
       </c>
-      <c r="G2" s="48"/>
-      <c r="H2" s="48"/>
+      <c r="G2" s="49"/>
+      <c r="H2" s="49"/>
     </row>
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B3" s="49"/>
+      <c r="B3" s="50"/>
       <c r="C3" s="35">
         <v>45291</v>
       </c>
@@ -4701,7 +5002,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3625BAB7-A2A5-4430-A1AB-4C5E3138421C}">
   <dimension ref="B3:G27"/>
   <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
@@ -4714,11 +5015,11 @@
   </cols>
   <sheetData>
     <row r="3" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B3" s="53" t="s">
+      <c r="B3" s="54" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="48"/>
-      <c r="D3" s="54"/>
+      <c r="C3" s="49"/>
+      <c r="D3" s="55"/>
     </row>
     <row r="4" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B4" s="40" t="s">
@@ -4758,11 +5059,11 @@
       <c r="D7" s="37"/>
     </row>
     <row r="8" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B8" s="50" t="s">
+      <c r="B8" s="51" t="s">
         <v>8</v>
       </c>
-      <c r="C8" s="51"/>
-      <c r="D8" s="52"/>
+      <c r="C8" s="52"/>
+      <c r="D8" s="53"/>
     </row>
     <row r="9" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B9" s="40" t="s">
@@ -4878,283 +5179,6 @@
     <mergeCell ref="B8:D8"/>
     <mergeCell ref="B3:D3"/>
   </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3E9C427A-629E-4C27-87B4-21766E37E9D1}">
-  <dimension ref="A2:E23"/>
-  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="2.33203125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="56" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.44140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="18" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.88671875" style="1"/>
-    <col min="7" max="7" width="5.44140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="16384" width="8.88671875" style="1"/>
-  </cols>
-  <sheetData>
-    <row r="2" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B2" s="42" t="s">
-        <v>79</v>
-      </c>
-      <c r="C2" s="43">
-        <v>46387</v>
-      </c>
-      <c r="D2" s="43">
-        <f>EDATE(C2,12)</f>
-        <v>46752</v>
-      </c>
-      <c r="E2" s="43">
-        <f>EDATE(D2,12)</f>
-        <v>47118</v>
-      </c>
-    </row>
-    <row r="3" spans="2:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B3" s="20" t="s">
-        <v>25</v>
-      </c>
-      <c r="C3" s="21"/>
-      <c r="D3" s="21"/>
-      <c r="E3" s="21"/>
-    </row>
-    <row r="4" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B4" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="C4" s="1">
-        <f>'Raw Data '!G3*(1+Assumptions!C5)</f>
-        <v>1358.5600000000002</v>
-      </c>
-      <c r="D4" s="11">
-        <f>C4*(1+Assumptions!C5)</f>
-        <v>1521.5872000000004</v>
-      </c>
-      <c r="E4" s="11">
-        <f>D4*(1+Assumptions!C5)</f>
-        <v>1704.1776640000005</v>
-      </c>
-    </row>
-    <row r="5" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B5" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="C5" s="19">
-        <f>'Raw Data '!G4*(1+Assumptions!C6)</f>
-        <v>182.35018466611703</v>
-      </c>
-      <c r="D5" s="19">
-        <f>C5*(1+Assumptions!C6)</f>
-        <v>185.99718835943938</v>
-      </c>
-      <c r="E5" s="19">
-        <f>D5*(1+Assumptions!C6)</f>
-        <v>189.71713212662817</v>
-      </c>
-    </row>
-    <row r="6" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B6" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="C6" s="19">
-        <f>C4*C5/10</f>
-        <v>24773.366687999998</v>
-      </c>
-      <c r="D6" s="19">
-        <f>D4*D5/10</f>
-        <v>28301.094104371201</v>
-      </c>
-      <c r="E6" s="19">
-        <f>E4*E5/10</f>
-        <v>32331.169904833667</v>
-      </c>
-    </row>
-    <row r="7" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B7" s="17" t="s">
-        <v>83</v>
-      </c>
-      <c r="C7" s="18"/>
-      <c r="D7" s="18"/>
-      <c r="E7" s="18"/>
-    </row>
-    <row r="8" spans="2:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B8" s="20" t="s">
-        <v>25</v>
-      </c>
-      <c r="C8" s="21"/>
-      <c r="D8" s="21"/>
-      <c r="E8" s="21"/>
-    </row>
-    <row r="9" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B9" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="C9" s="11">
-        <f>('Raw Data '!G3-'Raw Data '!F3)*'Raw Data '!F4</f>
-        <v>15842.356316725978</v>
-      </c>
-      <c r="D9" s="11">
-        <f>(D4-C4)*C5</f>
-        <v>29728.040025600036</v>
-      </c>
-      <c r="E9" s="11">
-        <f>(E4-D4)*D5</f>
-        <v>33961.312925245453</v>
-      </c>
-    </row>
-    <row r="10" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B10" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="C10" s="11">
-        <f>('Raw Data '!G4-'Raw Data '!F4)*'Raw Data '!G3</f>
-        <v>934.84368327397806</v>
-      </c>
-      <c r="D10" s="11">
-        <f>(D5-C5)*D4</f>
-        <v>5549.2341381120095</v>
-      </c>
-      <c r="E10" s="11">
-        <f>(E5-D5)*E4</f>
-        <v>6339.4450793791621</v>
-      </c>
-    </row>
-    <row r="11" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B11" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="C11" s="11">
-        <f>C9+C10</f>
-        <v>16777.199999999957</v>
-      </c>
-      <c r="D11" s="11">
-        <f t="shared" ref="D11:E11" si="0">D9+D10</f>
-        <v>35277.274163712049</v>
-      </c>
-      <c r="E11" s="11">
-        <f t="shared" si="0"/>
-        <v>40300.758004624615</v>
-      </c>
-    </row>
-    <row r="12" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B12" s="17" t="s">
-        <v>84</v>
-      </c>
-      <c r="C12" s="18"/>
-      <c r="D12" s="18"/>
-      <c r="E12" s="18"/>
-    </row>
-    <row r="13" spans="2:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B13" s="20" t="s">
-        <v>25</v>
-      </c>
-      <c r="C13" s="21"/>
-      <c r="D13" s="21"/>
-      <c r="E13" s="21"/>
-    </row>
-    <row r="14" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B14" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="C14" s="19">
-        <f>C6*Assumptions!C10</f>
-        <v>11148.0150096</v>
-      </c>
-      <c r="D14" s="19">
-        <f>$D$6*Assumptions!C10</f>
-        <v>12735.492346967041</v>
-      </c>
-      <c r="E14" s="19">
-        <f>$E$6*Assumptions!C10</f>
-        <v>14549.02645717515</v>
-      </c>
-    </row>
-    <row r="15" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B15" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="C15" s="19">
-        <f>C6*Assumptions!C11</f>
-        <v>2725.07033568</v>
-      </c>
-      <c r="D15" s="19">
-        <f>$D$6*Assumptions!C11</f>
-        <v>3113.1203514808321</v>
-      </c>
-      <c r="E15" s="19">
-        <f>$E$6*Assumptions!C11</f>
-        <v>3556.4286895317032</v>
-      </c>
-    </row>
-    <row r="16" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B16" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="C16" s="19">
-        <f>C6*Assumptions!C12</f>
-        <v>5202.4070044799992</v>
-      </c>
-      <c r="D16" s="19">
-        <f>$D$6*Assumptions!C12</f>
-        <v>5943.2297619179517</v>
-      </c>
-      <c r="E16" s="19">
-        <f>$E$6*Assumptions!C12</f>
-        <v>6789.5456800150696</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B17" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="C17" s="19">
-        <f>C6-(C14+C15+C16)</f>
-        <v>5697.8743382399989</v>
-      </c>
-      <c r="D17" s="19">
-        <f>D6-(D14+D15+D16)</f>
-        <v>6509.2516440053769</v>
-      </c>
-      <c r="E17" s="19">
-        <f>E6-(E14+E15+E16)</f>
-        <v>7436.1690781117431</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B18" s="22" t="s">
-        <v>89</v>
-      </c>
-      <c r="C18" s="23">
-        <f>C17/C6</f>
-        <v>0.22999999999999998</v>
-      </c>
-      <c r="D18" s="23">
-        <f>D17/D6</f>
-        <v>0.23</v>
-      </c>
-      <c r="E18" s="23">
-        <f>E17/E6</f>
-        <v>0.22999999999999998</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" ht="16.2" thickTop="1" x14ac:dyDescent="0.3"/>
-    <row r="21" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B21"/>
-      <c r="C21" s="27" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" ht="29.4" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A23" t="s">
-        <v>103</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="12" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -5411,16 +5435,16 @@
       <c r="B1" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="E1" s="55" t="str">
+      <c r="E1" s="56" t="str">
         <f>IF(B2&lt;&gt;B3, "A NEW VERSION OF THE WORKSHEET IS AVAILABLE", "")</f>
         <v/>
       </c>
-      <c r="F1" s="55"/>
-      <c r="G1" s="55"/>
-      <c r="H1" s="55"/>
-      <c r="I1" s="55"/>
-      <c r="J1" s="55"/>
-      <c r="K1" s="55"/>
+      <c r="F1" s="56"/>
+      <c r="G1" s="56"/>
+      <c r="H1" s="56"/>
+      <c r="I1" s="56"/>
+      <c r="J1" s="56"/>
+      <c r="K1" s="56"/>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" s="5" t="s">
@@ -5429,15 +5453,15 @@
       <c r="B2" s="6">
         <v>2.1</v>
       </c>
-      <c r="E2" s="56" t="s">
+      <c r="E2" s="57" t="s">
         <v>29</v>
       </c>
-      <c r="F2" s="56"/>
-      <c r="G2" s="56"/>
-      <c r="H2" s="56"/>
-      <c r="I2" s="56"/>
-      <c r="J2" s="56"/>
-      <c r="K2" s="56"/>
+      <c r="F2" s="57"/>
+      <c r="G2" s="57"/>
+      <c r="H2" s="57"/>
+      <c r="I2" s="57"/>
+      <c r="J2" s="57"/>
+      <c r="K2" s="57"/>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="s">

--- a/Varun Beverages.xlsx
+++ b/Varun Beverages.xlsx
@@ -8,16 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\varun beverages\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7555BAD2-A567-48AC-BD5F-96AF8A2B417B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B60F27C1-27E7-4B59-8BA9-178BFA11E926}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{DC4468AB-D1B0-41A7-9804-C13850339D52}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{DC4468AB-D1B0-41A7-9804-C13850339D52}"/>
   </bookViews>
   <sheets>
     <sheet name="Summary " sheetId="7" r:id="rId1"/>
-    <sheet name="Calculations " sheetId="4" r:id="rId2"/>
-    <sheet name="Dashboard " sheetId="5" r:id="rId3"/>
-    <sheet name="Ratio Analysis" sheetId="6" r:id="rId4"/>
-    <sheet name="Assumptions" sheetId="1" r:id="rId5"/>
+    <sheet name="Dashboard " sheetId="5" r:id="rId2"/>
+    <sheet name="Ratio Analysis" sheetId="6" r:id="rId3"/>
+    <sheet name="Assumptions" sheetId="1" r:id="rId4"/>
+    <sheet name="Calculations " sheetId="4" r:id="rId5"/>
     <sheet name="Raw Data " sheetId="2" r:id="rId6"/>
     <sheet name="Data Sheet " sheetId="3" r:id="rId7"/>
   </sheets>
@@ -4335,283 +4335,6 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3E9C427A-629E-4C27-87B4-21766E37E9D1}">
-  <dimension ref="A2:E23"/>
-  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="2.33203125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="56" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.44140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="18" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.88671875" style="1"/>
-    <col min="7" max="7" width="5.44140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="16384" width="8.88671875" style="1"/>
-  </cols>
-  <sheetData>
-    <row r="2" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B2" s="42" t="s">
-        <v>79</v>
-      </c>
-      <c r="C2" s="43">
-        <v>46387</v>
-      </c>
-      <c r="D2" s="43">
-        <f>EDATE(C2,12)</f>
-        <v>46752</v>
-      </c>
-      <c r="E2" s="43">
-        <f>EDATE(D2,12)</f>
-        <v>47118</v>
-      </c>
-    </row>
-    <row r="3" spans="2:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B3" s="20" t="s">
-        <v>25</v>
-      </c>
-      <c r="C3" s="21"/>
-      <c r="D3" s="21"/>
-      <c r="E3" s="21"/>
-    </row>
-    <row r="4" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B4" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="C4" s="1">
-        <f>'Raw Data '!G3*(1+Assumptions!C5)</f>
-        <v>1358.5600000000002</v>
-      </c>
-      <c r="D4" s="11">
-        <f>C4*(1+Assumptions!C5)</f>
-        <v>1521.5872000000004</v>
-      </c>
-      <c r="E4" s="11">
-        <f>D4*(1+Assumptions!C5)</f>
-        <v>1704.1776640000005</v>
-      </c>
-    </row>
-    <row r="5" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B5" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="C5" s="19">
-        <f>'Raw Data '!G4*(1+Assumptions!C6)</f>
-        <v>182.35018466611703</v>
-      </c>
-      <c r="D5" s="19">
-        <f>C5*(1+Assumptions!C6)</f>
-        <v>185.99718835943938</v>
-      </c>
-      <c r="E5" s="19">
-        <f>D5*(1+Assumptions!C6)</f>
-        <v>189.71713212662817</v>
-      </c>
-    </row>
-    <row r="6" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B6" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="C6" s="19">
-        <f>C4*C5/10</f>
-        <v>24773.366687999998</v>
-      </c>
-      <c r="D6" s="19">
-        <f>D4*D5/10</f>
-        <v>28301.094104371201</v>
-      </c>
-      <c r="E6" s="19">
-        <f>E4*E5/10</f>
-        <v>32331.169904833667</v>
-      </c>
-    </row>
-    <row r="7" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B7" s="17" t="s">
-        <v>83</v>
-      </c>
-      <c r="C7" s="18"/>
-      <c r="D7" s="18"/>
-      <c r="E7" s="18"/>
-    </row>
-    <row r="8" spans="2:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B8" s="20" t="s">
-        <v>25</v>
-      </c>
-      <c r="C8" s="21"/>
-      <c r="D8" s="21"/>
-      <c r="E8" s="21"/>
-    </row>
-    <row r="9" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B9" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="C9" s="11">
-        <f>('Raw Data '!G3-'Raw Data '!F3)*'Raw Data '!F4</f>
-        <v>15842.356316725978</v>
-      </c>
-      <c r="D9" s="11">
-        <f>(D4-C4)*C5</f>
-        <v>29728.040025600036</v>
-      </c>
-      <c r="E9" s="11">
-        <f>(E4-D4)*D5</f>
-        <v>33961.312925245453</v>
-      </c>
-    </row>
-    <row r="10" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B10" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="C10" s="11">
-        <f>('Raw Data '!G4-'Raw Data '!F4)*'Raw Data '!G3</f>
-        <v>934.84368327397806</v>
-      </c>
-      <c r="D10" s="11">
-        <f>(D5-C5)*D4</f>
-        <v>5549.2341381120095</v>
-      </c>
-      <c r="E10" s="11">
-        <f>(E5-D5)*E4</f>
-        <v>6339.4450793791621</v>
-      </c>
-    </row>
-    <row r="11" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B11" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="C11" s="11">
-        <f>C9+C10</f>
-        <v>16777.199999999957</v>
-      </c>
-      <c r="D11" s="11">
-        <f t="shared" ref="D11:E11" si="0">D9+D10</f>
-        <v>35277.274163712049</v>
-      </c>
-      <c r="E11" s="11">
-        <f t="shared" si="0"/>
-        <v>40300.758004624615</v>
-      </c>
-    </row>
-    <row r="12" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B12" s="17" t="s">
-        <v>84</v>
-      </c>
-      <c r="C12" s="18"/>
-      <c r="D12" s="18"/>
-      <c r="E12" s="18"/>
-    </row>
-    <row r="13" spans="2:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B13" s="20" t="s">
-        <v>25</v>
-      </c>
-      <c r="C13" s="21"/>
-      <c r="D13" s="21"/>
-      <c r="E13" s="21"/>
-    </row>
-    <row r="14" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B14" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="C14" s="19">
-        <f>C6*Assumptions!C10</f>
-        <v>11148.0150096</v>
-      </c>
-      <c r="D14" s="19">
-        <f>$D$6*Assumptions!C10</f>
-        <v>12735.492346967041</v>
-      </c>
-      <c r="E14" s="19">
-        <f>$E$6*Assumptions!C10</f>
-        <v>14549.02645717515</v>
-      </c>
-    </row>
-    <row r="15" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B15" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="C15" s="19">
-        <f>C6*Assumptions!C11</f>
-        <v>2725.07033568</v>
-      </c>
-      <c r="D15" s="19">
-        <f>$D$6*Assumptions!C11</f>
-        <v>3113.1203514808321</v>
-      </c>
-      <c r="E15" s="19">
-        <f>$E$6*Assumptions!C11</f>
-        <v>3556.4286895317032</v>
-      </c>
-    </row>
-    <row r="16" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B16" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="C16" s="19">
-        <f>C6*Assumptions!C12</f>
-        <v>5202.4070044799992</v>
-      </c>
-      <c r="D16" s="19">
-        <f>$D$6*Assumptions!C12</f>
-        <v>5943.2297619179517</v>
-      </c>
-      <c r="E16" s="19">
-        <f>$E$6*Assumptions!C12</f>
-        <v>6789.5456800150696</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B17" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="C17" s="19">
-        <f>C6-(C14+C15+C16)</f>
-        <v>5697.8743382399989</v>
-      </c>
-      <c r="D17" s="19">
-        <f>D6-(D14+D15+D16)</f>
-        <v>6509.2516440053769</v>
-      </c>
-      <c r="E17" s="19">
-        <f>E6-(E14+E15+E16)</f>
-        <v>7436.1690781117431</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B18" s="22" t="s">
-        <v>89</v>
-      </c>
-      <c r="C18" s="23">
-        <f>C17/C6</f>
-        <v>0.22999999999999998</v>
-      </c>
-      <c r="D18" s="23">
-        <f>D17/D6</f>
-        <v>0.23</v>
-      </c>
-      <c r="E18" s="23">
-        <f>E17/E6</f>
-        <v>0.22999999999999998</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" ht="16.2" thickTop="1" x14ac:dyDescent="0.3"/>
-    <row r="21" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B21"/>
-      <c r="C21" s="27" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" ht="29.4" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A23" t="s">
-        <v>103</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="12" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4CE63FB2-9482-46F5-96F9-055ACEF11988}">
   <dimension ref="R10:W16"/>
   <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
@@ -4771,7 +4494,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C4ADC91-F7B2-4C44-ADE9-BE109BA4B8AA}">
   <dimension ref="B2:I10"/>
   <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
@@ -5002,7 +4725,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3625BAB7-A2A5-4430-A1AB-4C5E3138421C}">
   <dimension ref="B3:G27"/>
   <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
@@ -5179,6 +4902,283 @@
     <mergeCell ref="B8:D8"/>
     <mergeCell ref="B3:D3"/>
   </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3E9C427A-629E-4C27-87B4-21766E37E9D1}">
+  <dimension ref="A2:E23"/>
+  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="2.33203125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="56" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="18" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.88671875" style="1"/>
+    <col min="7" max="7" width="5.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="16384" width="8.88671875" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B2" s="42" t="s">
+        <v>79</v>
+      </c>
+      <c r="C2" s="43">
+        <v>46387</v>
+      </c>
+      <c r="D2" s="43">
+        <f>EDATE(C2,12)</f>
+        <v>46752</v>
+      </c>
+      <c r="E2" s="43">
+        <f>EDATE(D2,12)</f>
+        <v>47118</v>
+      </c>
+    </row>
+    <row r="3" spans="2:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B3" s="20" t="s">
+        <v>25</v>
+      </c>
+      <c r="C3" s="21"/>
+      <c r="D3" s="21"/>
+      <c r="E3" s="21"/>
+    </row>
+    <row r="4" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B4" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="C4" s="1">
+        <f>'Raw Data '!G3*(1+Assumptions!C5)</f>
+        <v>1358.5600000000002</v>
+      </c>
+      <c r="D4" s="11">
+        <f>C4*(1+Assumptions!C5)</f>
+        <v>1521.5872000000004</v>
+      </c>
+      <c r="E4" s="11">
+        <f>D4*(1+Assumptions!C5)</f>
+        <v>1704.1776640000005</v>
+      </c>
+    </row>
+    <row r="5" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B5" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="C5" s="19">
+        <f>'Raw Data '!G4*(1+Assumptions!C6)</f>
+        <v>182.35018466611703</v>
+      </c>
+      <c r="D5" s="19">
+        <f>C5*(1+Assumptions!C6)</f>
+        <v>185.99718835943938</v>
+      </c>
+      <c r="E5" s="19">
+        <f>D5*(1+Assumptions!C6)</f>
+        <v>189.71713212662817</v>
+      </c>
+    </row>
+    <row r="6" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B6" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="C6" s="19">
+        <f>C4*C5/10</f>
+        <v>24773.366687999998</v>
+      </c>
+      <c r="D6" s="19">
+        <f>D4*D5/10</f>
+        <v>28301.094104371201</v>
+      </c>
+      <c r="E6" s="19">
+        <f>E4*E5/10</f>
+        <v>32331.169904833667</v>
+      </c>
+    </row>
+    <row r="7" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B7" s="17" t="s">
+        <v>83</v>
+      </c>
+      <c r="C7" s="18"/>
+      <c r="D7" s="18"/>
+      <c r="E7" s="18"/>
+    </row>
+    <row r="8" spans="2:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B8" s="20" t="s">
+        <v>25</v>
+      </c>
+      <c r="C8" s="21"/>
+      <c r="D8" s="21"/>
+      <c r="E8" s="21"/>
+    </row>
+    <row r="9" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B9" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="C9" s="11">
+        <f>('Raw Data '!G3-'Raw Data '!F3)*'Raw Data '!F4</f>
+        <v>15842.356316725978</v>
+      </c>
+      <c r="D9" s="11">
+        <f>(D4-C4)*C5</f>
+        <v>29728.040025600036</v>
+      </c>
+      <c r="E9" s="11">
+        <f>(E4-D4)*D5</f>
+        <v>33961.312925245453</v>
+      </c>
+    </row>
+    <row r="10" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B10" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="C10" s="11">
+        <f>('Raw Data '!G4-'Raw Data '!F4)*'Raw Data '!G3</f>
+        <v>934.84368327397806</v>
+      </c>
+      <c r="D10" s="11">
+        <f>(D5-C5)*D4</f>
+        <v>5549.2341381120095</v>
+      </c>
+      <c r="E10" s="11">
+        <f>(E5-D5)*E4</f>
+        <v>6339.4450793791621</v>
+      </c>
+    </row>
+    <row r="11" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B11" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="C11" s="11">
+        <f>C9+C10</f>
+        <v>16777.199999999957</v>
+      </c>
+      <c r="D11" s="11">
+        <f t="shared" ref="D11:E11" si="0">D9+D10</f>
+        <v>35277.274163712049</v>
+      </c>
+      <c r="E11" s="11">
+        <f t="shared" si="0"/>
+        <v>40300.758004624615</v>
+      </c>
+    </row>
+    <row r="12" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B12" s="17" t="s">
+        <v>84</v>
+      </c>
+      <c r="C12" s="18"/>
+      <c r="D12" s="18"/>
+      <c r="E12" s="18"/>
+    </row>
+    <row r="13" spans="2:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B13" s="20" t="s">
+        <v>25</v>
+      </c>
+      <c r="C13" s="21"/>
+      <c r="D13" s="21"/>
+      <c r="E13" s="21"/>
+    </row>
+    <row r="14" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B14" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="C14" s="19">
+        <f>C6*Assumptions!C10</f>
+        <v>11148.0150096</v>
+      </c>
+      <c r="D14" s="19">
+        <f>$D$6*Assumptions!C10</f>
+        <v>12735.492346967041</v>
+      </c>
+      <c r="E14" s="19">
+        <f>$E$6*Assumptions!C10</f>
+        <v>14549.02645717515</v>
+      </c>
+    </row>
+    <row r="15" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B15" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="C15" s="19">
+        <f>C6*Assumptions!C11</f>
+        <v>2725.07033568</v>
+      </c>
+      <c r="D15" s="19">
+        <f>$D$6*Assumptions!C11</f>
+        <v>3113.1203514808321</v>
+      </c>
+      <c r="E15" s="19">
+        <f>$E$6*Assumptions!C11</f>
+        <v>3556.4286895317032</v>
+      </c>
+    </row>
+    <row r="16" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B16" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="C16" s="19">
+        <f>C6*Assumptions!C12</f>
+        <v>5202.4070044799992</v>
+      </c>
+      <c r="D16" s="19">
+        <f>$D$6*Assumptions!C12</f>
+        <v>5943.2297619179517</v>
+      </c>
+      <c r="E16" s="19">
+        <f>$E$6*Assumptions!C12</f>
+        <v>6789.5456800150696</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B17" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="C17" s="19">
+        <f>C6-(C14+C15+C16)</f>
+        <v>5697.8743382399989</v>
+      </c>
+      <c r="D17" s="19">
+        <f>D6-(D14+D15+D16)</f>
+        <v>6509.2516440053769</v>
+      </c>
+      <c r="E17" s="19">
+        <f>E6-(E14+E15+E16)</f>
+        <v>7436.1690781117431</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B18" s="22" t="s">
+        <v>89</v>
+      </c>
+      <c r="C18" s="23">
+        <f>C17/C6</f>
+        <v>0.22999999999999998</v>
+      </c>
+      <c r="D18" s="23">
+        <f>D17/D6</f>
+        <v>0.23</v>
+      </c>
+      <c r="E18" s="23">
+        <f>E17/E6</f>
+        <v>0.22999999999999998</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" ht="16.2" thickTop="1" x14ac:dyDescent="0.3"/>
+    <row r="21" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B21"/>
+      <c r="C21" s="27" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" ht="29.4" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>103</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="12" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>

--- a/Varun Beverages.xlsx
+++ b/Varun Beverages.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\varun beverages\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B60F27C1-27E7-4B59-8BA9-178BFA11E926}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A2A8F41-96B9-4AF7-81F2-B3FE22131CDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{DC4468AB-D1B0-41A7-9804-C13850339D52}"/>
   </bookViews>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="105">
   <si>
     <t>Revenue Drivers (Operational Inputs)</t>
   </si>
@@ -351,12 +351,6 @@
   </si>
   <si>
     <t xml:space="preserve">Debt-to-equity  </t>
-  </si>
-  <si>
-    <t>COGS % test values</t>
-  </si>
-  <si>
-    <t>Volume Growth % test values</t>
   </si>
   <si>
     <t>EBITDA Sensitivity (₹ Cr): Volume Growth vs. COGS %</t>
@@ -709,18 +703,6 @@
     <xf numFmtId="9" fontId="4" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="13" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -733,7 +715,19 @@
     <xf numFmtId="0" fontId="13" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="43" fontId="6" fillId="0" borderId="0" xfId="4" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -4312,18 +4306,18 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B2" s="47" t="s">
-        <v>106</v>
-      </c>
-      <c r="C2" s="47"/>
-      <c r="D2" s="47"/>
-      <c r="E2" s="47"/>
-      <c r="F2" s="47"/>
-      <c r="G2" s="47"/>
-      <c r="H2" s="47"/>
-      <c r="I2" s="47"/>
-      <c r="J2" s="47"/>
-      <c r="K2" s="47"/>
+      <c r="B2" s="53" t="s">
+        <v>104</v>
+      </c>
+      <c r="C2" s="53"/>
+      <c r="D2" s="53"/>
+      <c r="E2" s="53"/>
+      <c r="F2" s="53"/>
+      <c r="G2" s="53"/>
+      <c r="H2" s="53"/>
+      <c r="I2" s="53"/>
+      <c r="J2" s="53"/>
+      <c r="K2" s="53"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -4344,14 +4338,14 @@
   </cols>
   <sheetData>
     <row r="10" spans="18:23" x14ac:dyDescent="0.3">
-      <c r="R10" s="48" t="s">
-        <v>104</v>
-      </c>
-      <c r="S10" s="48"/>
-      <c r="T10" s="48"/>
-      <c r="U10" s="48"/>
-      <c r="V10" s="48"/>
-      <c r="W10" s="48"/>
+      <c r="R10" s="54" t="s">
+        <v>102</v>
+      </c>
+      <c r="S10" s="54"/>
+      <c r="T10" s="54"/>
+      <c r="U10" s="54"/>
+      <c r="V10" s="54"/>
+      <c r="W10" s="54"/>
     </row>
     <row r="11" spans="18:23" x14ac:dyDescent="0.3">
       <c r="R11" s="28">
@@ -4506,22 +4500,22 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B2" s="49" t="s">
+      <c r="B2" s="51" t="s">
         <v>95</v>
       </c>
-      <c r="C2" s="49" t="s">
+      <c r="C2" s="51" t="s">
         <v>93</v>
       </c>
-      <c r="D2" s="49"/>
-      <c r="E2" s="49"/>
-      <c r="F2" s="49" t="s">
+      <c r="D2" s="51"/>
+      <c r="E2" s="51"/>
+      <c r="F2" s="51" t="s">
         <v>94</v>
       </c>
-      <c r="G2" s="49"/>
-      <c r="H2" s="49"/>
+      <c r="G2" s="51"/>
+      <c r="H2" s="51"/>
     </row>
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B3" s="50"/>
+      <c r="B3" s="55"/>
       <c r="C3" s="35">
         <v>45291</v>
       </c>
@@ -4680,13 +4674,13 @@
         <v>0.12810758630552588</v>
       </c>
       <c r="F9" s="31" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="G9" s="31" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="H9" s="31" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
     </row>
     <row r="10" spans="2:9" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
@@ -4706,13 +4700,13 @@
         <v>0.15509150250016598</v>
       </c>
       <c r="F10" s="34" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="G10" s="34" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="H10" s="34" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
     </row>
   </sheetData>
@@ -4738,11 +4732,11 @@
   </cols>
   <sheetData>
     <row r="3" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B3" s="54" t="s">
+      <c r="B3" s="50" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="49"/>
-      <c r="D3" s="55"/>
+      <c r="C3" s="51"/>
+      <c r="D3" s="52"/>
     </row>
     <row r="4" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B4" s="40" t="s">
@@ -4782,11 +4776,11 @@
       <c r="D7" s="37"/>
     </row>
     <row r="8" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B8" s="51" t="s">
+      <c r="B8" s="47" t="s">
         <v>8</v>
       </c>
-      <c r="C8" s="52"/>
-      <c r="D8" s="53"/>
+      <c r="C8" s="48"/>
+      <c r="D8" s="49"/>
     </row>
     <row r="9" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B9" s="40" t="s">
@@ -5165,17 +5159,13 @@
       </c>
     </row>
     <row r="19" spans="1:5" ht="16.2" thickTop="1" x14ac:dyDescent="0.3"/>
-    <row r="21" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B21"/>
-      <c r="C21" s="27" t="s">
-        <v>102</v>
-      </c>
+      <c r="C21" s="27"/>
     </row>
     <row r="22" spans="1:5" ht="29.4" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="23" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A23" t="s">
-        <v>103</v>
-      </c>
+      <c r="A23"/>
     </row>
   </sheetData>
   <phoneticPr fontId="12" type="noConversion"/>

--- a/Varun Beverages.xlsx
+++ b/Varun Beverages.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\varun beverages\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A2A8F41-96B9-4AF7-81F2-B3FE22131CDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{088EDBA1-AE2C-4648-B40E-25B5868C0948}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{DC4468AB-D1B0-41A7-9804-C13850339D52}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{DC4468AB-D1B0-41A7-9804-C13850339D52}"/>
   </bookViews>
   <sheets>
     <sheet name="Summary " sheetId="7" r:id="rId1"/>
